--- a/maliye/011_ 2018-2023_ Kira-Mali_Hesaplar/010_ 2016-2023 bankadanKira.xlsx
+++ b/maliye/011_ 2018-2023_ Kira-Mali_Hesaplar/010_ 2016-2023 bankadanKira.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\tdy\2007-2023_ Hesap-Toplamlar\011_ 2018-2023_ Kira-Mali_Hesaplar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\maliye\011_ 2018-2023_ Kira-Mali_Hesaplar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B962786C-B9E9-464F-B436-04010360E769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22768FED-ED15-4338-BCC6-4FE18933B6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CD6DC27-3A51-466C-87F3-E3631C0927D1}"/>
+    <workbookView xWindow="7545" yWindow="3225" windowWidth="19905" windowHeight="12270" xr2:uid="{7CD6DC27-3A51-466C-87F3-E3631C0927D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="150">
   <si>
     <t>22/12/2016</t>
   </si>
@@ -471,16 +471,22 @@
     <t>VERGİ DAİRESİ ADRES KODLARI</t>
   </si>
   <si>
-    <t>Merdal Kipel</t>
-  </si>
-  <si>
-    <t>Süleyman Akan</t>
-  </si>
-  <si>
     <t>hesap</t>
   </si>
   <si>
     <t>hesap no</t>
+  </si>
+  <si>
+    <t>Merdal Kipel                         umut kapatılan ortak hesap</t>
+  </si>
+  <si>
+    <t>Süleyman Akan                    umut kapatılan ortak hesap</t>
+  </si>
+  <si>
+    <t>Cihan ÇAM                    umut kapatılan ana hesap</t>
+  </si>
+  <si>
+    <t>Salih ANT      umut kapatılan ana hesap    SALİH ANT*0111*2024 yılı iş yeri kira bedeli*1307883986*FAST</t>
   </si>
 </sst>
 </file>
@@ -489,9 +495,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.00"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,6 +597,15 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -675,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -790,27 +805,55 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1126,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13DCE68-38B3-4CBB-8CF9-FB77F953DE73}">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" style="71" bestFit="1" customWidth="1"/>
@@ -1977,7 +2020,7 @@
       <c r="D72" s="13"/>
       <c r="E72" s="13"/>
       <c r="F72" s="13"/>
-      <c r="G72" s="11"/>
+      <c r="G72" s="81"/>
       <c r="H72" s="12"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -2162,7 +2205,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B85" s="74"/>
       <c r="C85" s="28" t="s">
@@ -2778,16 +2821,16 @@
     <row r="128" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="67"/>
       <c r="C128" s="4">
-        <f>D139</f>
-        <v>85000</v>
+        <f>D140</f>
+        <v>142000</v>
       </c>
       <c r="D128" s="57">
         <f>C128/80*100</f>
-        <v>106250</v>
+        <v>177500</v>
       </c>
       <c r="E128" s="26">
-        <f>E139</f>
-        <v>17000</v>
+        <f>E140</f>
+        <v>28400</v>
       </c>
       <c r="F128" s="13"/>
       <c r="G128" s="11" t="s">
@@ -2798,8 +2841,8 @@
       <c r="A129" s="67"/>
       <c r="C129" s="4"/>
       <c r="D129" s="57">
-        <f>D153</f>
-        <v>33000</v>
+        <f>D154</f>
+        <v>6000</v>
       </c>
       <c r="E129" s="26"/>
       <c r="F129" s="13"/>
@@ -2813,11 +2856,11 @@
       <c r="C130" s="61"/>
       <c r="D130" s="62">
         <f>SUM(D128:D129)</f>
-        <v>139250</v>
+        <v>183500</v>
       </c>
       <c r="E130" s="63">
         <f>E128</f>
-        <v>17000</v>
+        <v>28400</v>
       </c>
       <c r="F130" s="64"/>
       <c r="G130" s="60" t="s">
@@ -2828,65 +2871,92 @@
       <c r="A131" s="67"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B132" s="74"/>
-      <c r="C132" s="28" t="s">
+      <c r="B132" s="88"/>
+      <c r="C132" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="D132" s="29" t="s">
+      <c r="D132" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="E132" s="30" t="s">
+      <c r="E132" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="F132" s="13"/>
-      <c r="G132" s="53" t="s">
+      <c r="F132" s="82"/>
+      <c r="G132" s="54" t="s">
         <v>126</v>
       </c>
       <c r="H132" s="12"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B133" s="70">
+      <c r="B133" s="83">
+        <v>45299</v>
+      </c>
+      <c r="C133" s="84">
+        <f>D133+E133</f>
+        <v>28800</v>
+      </c>
+      <c r="D133" s="92">
+        <v>24000</v>
+      </c>
+      <c r="E133" s="85">
+        <f>D133*20/100</f>
+        <v>4800</v>
+      </c>
+      <c r="F133" s="86"/>
+      <c r="G133" s="87" t="s">
+        <v>149</v>
+      </c>
+      <c r="H133" s="12"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B134" s="70">
         <v>45397</v>
       </c>
-      <c r="C133" s="66">
-        <f>D133+E133</f>
+      <c r="C134" s="66">
+        <f>D134+E134</f>
         <v>102000</v>
       </c>
-      <c r="D133" s="27">
+      <c r="D134" s="27">
         <v>85000</v>
       </c>
-      <c r="E133" s="10">
-        <f>D133*20/100</f>
+      <c r="E134" s="10">
+        <f>D134*20/100</f>
         <v>17000</v>
       </c>
-      <c r="F133" s="13"/>
-      <c r="G133" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H133" s="12"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B134" s="70"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
       <c r="F134" s="13"/>
-      <c r="G134" s="11"/>
+      <c r="G134" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="H134" s="12"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B135" s="70"/>
-      <c r="D135" s="13"/>
-      <c r="E135" s="13"/>
+      <c r="B135" s="70">
+        <v>45404</v>
+      </c>
+      <c r="C135" s="66">
+        <f>D135+E135</f>
+        <v>39600</v>
+      </c>
+      <c r="D135" s="27">
+        <v>33000</v>
+      </c>
+      <c r="E135" s="10">
+        <f>D135*20/100</f>
+        <v>6600</v>
+      </c>
       <c r="F135" s="13"/>
-      <c r="G135" s="11"/>
+      <c r="G135" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="H135" s="12"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B136" s="73"/>
-      <c r="D136" s="17"/>
+      <c r="B136" s="70"/>
+      <c r="D136" s="13"/>
       <c r="E136" s="13"/>
-      <c r="F136" s="16"/>
-      <c r="G136" s="3"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="11"/>
+      <c r="H136" s="12"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B137" s="73"/>
@@ -2895,66 +2965,55 @@
       <c r="F137" s="16"/>
       <c r="G137" s="3"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B139" s="78" t="s">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B138" s="73"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="3"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B140" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="68">
-        <f>SUM(C133:C138)</f>
-        <v>102000</v>
-      </c>
-      <c r="D139" s="68">
-        <f>SUM(D133:D138)</f>
-        <v>85000</v>
-      </c>
-      <c r="E139" s="68">
-        <f>SUM(E133:E138)</f>
-        <v>17000</v>
-      </c>
-      <c r="F139" s="69"/>
-      <c r="G139" s="69"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C140" s="12"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="58"/>
+      <c r="C140" s="68">
+        <f>SUM(C133:C139)</f>
+        <v>170400</v>
+      </c>
+      <c r="D140" s="68">
+        <f>SUM(D133:D139)</f>
+        <v>142000</v>
+      </c>
+      <c r="E140" s="68">
+        <f>SUM(E133:E139)</f>
+        <v>28400</v>
+      </c>
+      <c r="F140" s="69"/>
+      <c r="G140" s="69"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C141" s="20" t="s">
+      <c r="C141" s="12"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="58"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C142" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D141" s="2">
-        <f>SUM(D133:D135)</f>
-        <v>85000</v>
-      </c>
-      <c r="F141" s="58"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="19"/>
-      <c r="B142" s="74"/>
-      <c r="C142" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F142" s="16"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="12"/>
+      <c r="D142" s="2">
+        <f>SUM(D133:D136)</f>
+        <v>142000</v>
+      </c>
+      <c r="F142" s="58"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="19"/>
       <c r="B143" s="74"/>
       <c r="C143" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D143" s="2">
-        <f>SUM(D141:D142)</f>
-        <v>85000</v>
-      </c>
-      <c r="E143" s="27">
-        <f>D143/100*20</f>
-        <v>17000</v>
-      </c>
-      <c r="F143" s="58"/>
+        <v>95</v>
+      </c>
+      <c r="F143" s="16"/>
       <c r="G143" s="11"/>
       <c r="H143" s="12"/>
     </row>
@@ -2962,13 +3021,17 @@
       <c r="A144" s="19"/>
       <c r="B144" s="74"/>
       <c r="C144" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
+      </c>
+      <c r="D144" s="2">
+        <f>SUM(D142:D143)</f>
+        <v>142000</v>
       </c>
       <c r="E144" s="27">
         <f>D144/100*20</f>
-        <v>0</v>
-      </c>
-      <c r="F144" s="16"/>
+        <v>28400</v>
+      </c>
+      <c r="F144" s="58"/>
       <c r="G144" s="11"/>
       <c r="H144" s="12"/>
     </row>
@@ -2976,11 +3039,11 @@
       <c r="A145" s="19"/>
       <c r="B145" s="74"/>
       <c r="C145" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E145" s="31">
-        <f>E143-E144</f>
-        <v>17000</v>
+        <v>135</v>
+      </c>
+      <c r="E145" s="27">
+        <f>D145/100*20</f>
+        <v>0</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="11"/>
@@ -2989,6 +3052,13 @@
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="19"/>
       <c r="B146" s="74"/>
+      <c r="C146" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E146" s="31">
+        <f>E144-E145</f>
+        <v>28400</v>
+      </c>
       <c r="F146" s="16"/>
       <c r="G146" s="11"/>
       <c r="H146" s="12"/>
@@ -2996,38 +3066,37 @@
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="19"/>
       <c r="B147" s="74"/>
-      <c r="C147" s="20"/>
-      <c r="D147" s="23"/>
-      <c r="E147" s="13"/>
       <c r="F147" s="16"/>
-      <c r="G147" s="59" t="s">
+      <c r="G147" s="11"/>
+      <c r="H147" s="12"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="19"/>
+      <c r="B148" s="74"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="23"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="H147" s="12"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B148" s="70">
-        <v>45404</v>
-      </c>
-      <c r="D148" s="13">
-        <v>33000</v>
-      </c>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13">
-        <f>D148*0.2</f>
-        <v>6600</v>
-      </c>
-      <c r="G148" s="11" t="s">
-        <v>145</v>
-      </c>
       <c r="H148" s="12"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B149" s="70"/>
-      <c r="D149" s="13"/>
+      <c r="B149" s="70">
+        <v>45294</v>
+      </c>
+      <c r="D149" s="13">
+        <v>6000</v>
+      </c>
       <c r="E149" s="13"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="11"/>
+      <c r="F149" s="13">
+        <f>D149*0.2</f>
+        <v>1200</v>
+      </c>
+      <c r="G149" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="H149" s="12"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -3039,150 +3108,145 @@
       <c r="H150" s="12"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B151" s="73"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+      <c r="B151" s="70"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="13"/>
-      <c r="G151" s="3"/>
+      <c r="G151" s="11"/>
+      <c r="H151" s="12"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B152" s="73"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="13"/>
+      <c r="E152" s="2"/>
       <c r="F152" s="13"/>
       <c r="G152" s="3"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D153" s="56">
-        <f>SUM(D148:D152)</f>
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B155" s="70"/>
-      <c r="C155" s="10" t="s">
+      <c r="B153" s="73"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D154" s="56">
+        <f>SUM(D149:D153)</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B156" s="70"/>
+      <c r="C156" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D155" s="13" t="s">
+      <c r="D156" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E155" s="13"/>
-      <c r="F155" s="13"/>
-      <c r="G155" s="11"/>
-      <c r="H155" s="12"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B156" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="C156" s="37">
-        <f>D130</f>
-        <v>139250</v>
-      </c>
-      <c r="D156" s="32"/>
-      <c r="E156" s="33"/>
-      <c r="F156" s="17"/>
-      <c r="G156" s="18"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="12"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B157" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C157" s="51">
-        <v>0.15</v>
-      </c>
-      <c r="D157" s="32">
-        <f>C156*C157</f>
-        <v>20887.5</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C157" s="37">
+        <f>D130</f>
+        <v>183500</v>
+      </c>
+      <c r="D157" s="32"/>
       <c r="E157" s="33"/>
       <c r="F157" s="17"/>
       <c r="G157" s="18"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B158" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="C158" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="C158" s="51">
+        <v>0.15</v>
+      </c>
       <c r="D158" s="32">
-        <f>C156-D157</f>
-        <v>118362.5</v>
+        <f>C157*C158</f>
+        <v>27525</v>
       </c>
       <c r="E158" s="33"/>
       <c r="F158" s="17"/>
       <c r="G158" s="18"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B159" s="72"/>
+      <c r="B159" s="72" t="s">
+        <v>121</v>
+      </c>
       <c r="C159" s="19"/>
-      <c r="D159" s="32"/>
+      <c r="D159" s="32">
+        <f>C157-D158</f>
+        <v>155975</v>
+      </c>
       <c r="E159" s="33"/>
       <c r="F159" s="17"/>
       <c r="G159" s="18"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B160" s="71">
-        <v>100000</v>
-      </c>
-      <c r="C160" s="35">
-        <v>0.15</v>
-      </c>
-      <c r="D160" s="4">
-        <f>B160*C160</f>
-        <v>15000</v>
-      </c>
+      <c r="B160" s="72"/>
+      <c r="C160" s="19"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="33"/>
       <c r="F160" s="17"/>
       <c r="G160" s="18"/>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B161" s="71">
-        <v>39250</v>
+        <v>100000</v>
       </c>
       <c r="C161" s="35">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D161" s="4">
         <f>B161*C161</f>
-        <v>7850</v>
+        <v>15000</v>
       </c>
       <c r="E161" s="33"/>
       <c r="F161" s="17"/>
       <c r="G161" s="18"/>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B162" s="71">
+        <v>39250</v>
+      </c>
       <c r="C162" s="35">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="D162" s="4">
         <f>B162*C162</f>
-        <v>0</v>
+        <v>7850</v>
       </c>
       <c r="E162" s="33"/>
       <c r="F162" s="17"/>
       <c r="G162" s="18"/>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B163" s="71" t="s">
-        <v>109</v>
-      </c>
-      <c r="C163" s="4"/>
-      <c r="D163" s="43">
-        <f>SUM(D160:D162)</f>
-        <v>22850</v>
+      <c r="C163" s="35">
+        <v>0.27</v>
+      </c>
+      <c r="D163" s="4">
+        <f>B163*C163</f>
+        <v>0</v>
       </c>
       <c r="E163" s="33"/>
       <c r="F163" s="17"/>
       <c r="G163" s="18"/>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B164" s="72" t="s">
-        <v>123</v>
-      </c>
-      <c r="C164" s="19"/>
-      <c r="D164" s="32">
-        <f>E130</f>
-        <v>17000</v>
+      <c r="B164" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C164" s="4"/>
+      <c r="D164" s="43">
+        <f>SUM(D161:D163)</f>
+        <v>22850</v>
       </c>
       <c r="E164" s="33"/>
       <c r="F164" s="17"/>
@@ -3190,16 +3254,29 @@
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B165" s="72" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C165" s="19"/>
       <c r="D165" s="32">
-        <f>D163-D164</f>
-        <v>5850</v>
-      </c>
-      <c r="E165" s="32"/>
+        <f>E130</f>
+        <v>28400</v>
+      </c>
+      <c r="E165" s="33"/>
       <c r="F165" s="17"/>
       <c r="G165" s="18"/>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B166" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="C166" s="19"/>
+      <c r="D166" s="32">
+        <f>D164-D165</f>
+        <v>-5550</v>
+      </c>
+      <c r="E166" s="32"/>
+      <c r="F166" s="17"/>
+      <c r="G166" s="18"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:H109">
@@ -3321,7 +3398,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B8" s="74"/>
       <c r="C8" s="28" t="s">
